--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103612189</v>
+        <v>111974130</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NV om Gustavbacke, Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439539.6698141842</v>
+        <v>439390</v>
       </c>
       <c r="R2" t="n">
-        <v>6951909.137404581</v>
+        <v>6952167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +756,19 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -800,50 +789,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107422372</v>
+        <v>111974128</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439455.1147665676</v>
+        <v>439390</v>
       </c>
       <c r="R3" t="n">
-        <v>6952113.207300059</v>
+        <v>6952157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,66 +879,79 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107422371</v>
+        <v>111974133</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439556.3324289495</v>
+        <v>439390</v>
       </c>
       <c r="R4" t="n">
-        <v>6952015.374530006</v>
+        <v>6952220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,66 +994,79 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107422373</v>
+        <v>111974149</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439428.5602540535</v>
+        <v>439396</v>
       </c>
       <c r="R5" t="n">
-        <v>6952169.718310327</v>
+        <v>6952024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,22 +1093,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,53 +1109,57 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111974159</v>
+        <v>111974154</v>
       </c>
       <c r="B6" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1181,14 +1174,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aloppmoarna i SO, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439167</v>
+        <v>439254</v>
       </c>
       <c r="R6" t="n">
-        <v>6951949</v>
+        <v>6952041</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,15 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111974144</v>
+        <v>111974122</v>
       </c>
       <c r="B7" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1305,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439557</v>
+        <v>439233</v>
       </c>
       <c r="R7" t="n">
-        <v>6952048</v>
+        <v>6952154</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,15 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111974153</v>
+        <v>111974131</v>
       </c>
       <c r="B8" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1425,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439422</v>
+        <v>439387</v>
       </c>
       <c r="R8" t="n">
-        <v>6951955</v>
+        <v>6952179</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,37 +1479,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111974146</v>
+        <v>111974136</v>
       </c>
       <c r="B9" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1545,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439350</v>
+        <v>439426</v>
       </c>
       <c r="R9" t="n">
-        <v>6952064</v>
+        <v>6952166</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,15 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111974128</v>
+        <v>111974138</v>
       </c>
       <c r="B10" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,21 +1605,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1665,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439391</v>
+        <v>439542</v>
       </c>
       <c r="R10" t="n">
-        <v>6952158</v>
+        <v>6952103</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,37 +1709,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111974148</v>
+        <v>111974142</v>
       </c>
       <c r="B11" t="n">
-        <v>88180</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1785,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439399</v>
+        <v>439572</v>
       </c>
       <c r="R11" t="n">
-        <v>6952033</v>
+        <v>6952035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1856,15 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111974151</v>
+        <v>111974150</v>
       </c>
       <c r="B12" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,21 +1835,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1905,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439458</v>
+        <v>439432</v>
       </c>
       <c r="R12" t="n">
-        <v>6952019</v>
+        <v>6952011</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1976,37 +1939,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111974147</v>
+        <v>111974157</v>
       </c>
       <c r="B13" t="n">
-        <v>88180</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2025,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439342</v>
+        <v>439240</v>
       </c>
       <c r="R13" t="n">
-        <v>6952056</v>
+        <v>6951963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2096,15 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111974136</v>
+        <v>111974134</v>
       </c>
       <c r="B14" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,21 +2065,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2145,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439427</v>
+        <v>439400</v>
       </c>
       <c r="R14" t="n">
-        <v>6952166</v>
+        <v>6952207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,12 +2172,7 @@
         <v>111974143</v>
       </c>
       <c r="B15" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,7 +2216,7 @@
         <v>439562</v>
       </c>
       <c r="R15" t="n">
-        <v>6952046</v>
+        <v>6952045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2336,37 +2284,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111974127</v>
+        <v>111974153</v>
       </c>
       <c r="B16" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2385,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439300</v>
+        <v>439422</v>
       </c>
       <c r="R16" t="n">
-        <v>6952178</v>
+        <v>6951955</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2456,37 +2399,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111974145</v>
+        <v>103612133</v>
       </c>
       <c r="B17" t="n">
-        <v>88180</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2501,14 +2439,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439522</v>
+        <v>439344</v>
       </c>
       <c r="R17" t="n">
-        <v>6952046</v>
+        <v>6952209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2535,12 +2473,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2551,11 +2489,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2576,15 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111974123</v>
+        <v>107422373</v>
       </c>
       <c r="B18" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,26 +2537,17 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439235</v>
+        <v>439428</v>
       </c>
       <c r="R18" t="n">
-        <v>6952150</v>
+        <v>6952170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2655,12 +2574,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,40 +2590,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111974130</v>
+        <v>111974123</v>
       </c>
       <c r="B19" t="n">
-        <v>88637</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,34 +2617,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439389</v>
+        <v>439235</v>
       </c>
       <c r="R19" t="n">
-        <v>6952167</v>
+        <v>6952151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2786,14 +2700,6 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2815,37 +2721,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111974152</v>
+        <v>111974125</v>
       </c>
       <c r="B20" t="n">
-        <v>88180</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2864,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439458</v>
+        <v>439279</v>
       </c>
       <c r="R20" t="n">
-        <v>6952019</v>
+        <v>6952207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,37 +2836,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111974160</v>
+        <v>111974132</v>
       </c>
       <c r="B21" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2980,14 +2876,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aloppmoarna i SO, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439162</v>
+        <v>439385</v>
       </c>
       <c r="R21" t="n">
-        <v>6951961</v>
+        <v>6952196</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3055,15 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111974149</v>
+        <v>111974139</v>
       </c>
       <c r="B22" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,21 +2962,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3104,10 +2995,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439396</v>
+        <v>439585</v>
       </c>
       <c r="R22" t="n">
-        <v>6952023</v>
+        <v>6952093</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3175,37 +3066,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111974162</v>
+        <v>111974144</v>
       </c>
       <c r="B23" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3220,14 +3106,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aloppmoarna i SO, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439105</v>
+        <v>439557</v>
       </c>
       <c r="R23" t="n">
-        <v>6951960</v>
+        <v>6952049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3295,15 +3181,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111974135</v>
+        <v>111974151</v>
       </c>
       <c r="B24" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,21 +3192,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3344,10 +3225,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439406</v>
+        <v>439457</v>
       </c>
       <c r="R24" t="n">
-        <v>6952200</v>
+        <v>6952019</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3415,37 +3296,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111974137</v>
+        <v>111974161</v>
       </c>
       <c r="B25" t="n">
-        <v>88180</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3460,14 +3336,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Aloppmoarna i SO, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439438</v>
+        <v>439131</v>
       </c>
       <c r="R25" t="n">
-        <v>6952140</v>
+        <v>6951966</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3535,15 +3411,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111974138</v>
+        <v>103612134</v>
       </c>
       <c r="B26" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3551,21 +3422,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3580,14 +3451,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439542</v>
+        <v>439308</v>
       </c>
       <c r="R26" t="n">
-        <v>6952103</v>
+        <v>6952235</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3614,12 +3485,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3630,11 +3501,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3655,15 +3521,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111974142</v>
+        <v>103612136</v>
       </c>
       <c r="B27" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,21 +3532,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3700,14 +3561,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439572</v>
+        <v>439274</v>
       </c>
       <c r="R27" t="n">
-        <v>6952035</v>
+        <v>6952201</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3734,12 +3595,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3750,11 +3611,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3775,15 +3631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111974150</v>
+        <v>103612189</v>
       </c>
       <c r="B28" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3791,21 +3642,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3820,14 +3671,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439433</v>
+        <v>439539</v>
       </c>
       <c r="R28" t="n">
-        <v>6952011</v>
+        <v>6951909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3854,12 +3705,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,11 +3721,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3895,15 +3741,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111974129</v>
+        <v>111974124</v>
       </c>
       <c r="B29" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,21 +3752,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3944,10 +3785,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439389</v>
+        <v>439276</v>
       </c>
       <c r="R29" t="n">
-        <v>6952167</v>
+        <v>6952197</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4015,15 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111974131</v>
+        <v>111974146</v>
       </c>
       <c r="B30" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,21 +3867,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4064,10 +3900,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439387</v>
+        <v>439350</v>
       </c>
       <c r="R30" t="n">
-        <v>6952179</v>
+        <v>6952064</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4135,15 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111974132</v>
+        <v>111974160</v>
       </c>
       <c r="B31" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,21 +3982,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4180,14 +4011,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Aloppmoarna i SO, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439385</v>
+        <v>439162</v>
       </c>
       <c r="R31" t="n">
-        <v>6952196</v>
+        <v>6951960</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4255,15 +4086,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111974122</v>
+        <v>107422372</v>
       </c>
       <c r="B32" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4271,43 +4097,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439233</v>
+        <v>439455</v>
       </c>
       <c r="R32" t="n">
-        <v>6952154</v>
+        <v>6952113</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4334,12 +4151,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4350,40 +4167,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111974161</v>
+        <v>111974127</v>
       </c>
       <c r="B33" t="n">
-        <v>90808</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4391,21 +4194,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4420,14 +4223,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aloppmoarna i SO, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439131</v>
+        <v>439300</v>
       </c>
       <c r="R33" t="n">
-        <v>6951966</v>
+        <v>6952178</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4492,6 +4295,1598 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>111974140</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>439585</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6952093</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>111974159</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i SO, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>439166</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6951948</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>111974162</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i SO, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>439105</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6951960</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>111974129</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>439390</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6952167</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111974135</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>439406</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6952200</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111974126</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>439290</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6952209</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111974137</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>439438</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6952140</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>111974145</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>439522</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6952046</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>111974147</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>439342</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6952056</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>111974148</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>439399</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6952034</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>111974152</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>439457</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6952019</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>111974155</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>439255</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6952037</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>111974158</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>439236</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6951939</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>107422371</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>439557</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6952016</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974133</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974149</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974154</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974122</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974131</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1591,6 +1631,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974136</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974138</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1821,6 +1871,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974142</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,6 +1991,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974150</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974157</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2166,6 +2231,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974134</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2351,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974143</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2396,6 +2471,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974153</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2506,6 +2586,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103612133</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2603,6 +2688,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422373</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2718,6 +2808,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974123</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2833,6 +2928,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974125</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2948,6 +3048,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974132</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3063,6 +3168,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974139</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3178,6 +3288,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974144</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3293,6 +3408,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974151</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3408,6 +3528,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974161</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3518,6 +3643,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103612134</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3628,6 +3758,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103612136</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3738,6 +3873,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103612189</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3853,6 +3993,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974124</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3968,6 +4113,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974146</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4083,6 +4233,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974160</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4180,6 +4335,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422372</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4295,6 +4455,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974127</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4410,6 +4575,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974140</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4525,6 +4695,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974159</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4640,6 +4815,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974162</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4755,6 +4935,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974129</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4870,6 +5055,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974135</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4985,6 +5175,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974126</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5100,6 +5295,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974137</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5215,6 +5415,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974145</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5330,6 +5535,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974147</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5445,6 +5655,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974148</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5560,6 +5775,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974152</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5675,6 +5895,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974155</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5790,6 +6015,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974158</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5887,8 +6117,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107422371</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111974130</v>
+        <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>90932</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439390</v>
+        <v>439319</v>
       </c>
       <c r="R2" t="n">
-        <v>6952167</v>
+        <v>6952017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,92 +761,66 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # under gammal tallåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974130</t>
+          <t>https://artportalen.se/Sighting/135784573</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111974128</v>
+        <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>93213</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439390</v>
+        <v>439319</v>
       </c>
       <c r="R3" t="n">
-        <v>6952157</v>
+        <v>6952017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,40 +863,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974128</t>
+          <t>https://artportalen.se/Sighting/135784574</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111974133</v>
+        <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>92227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,43 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439390</v>
+        <v>439293</v>
       </c>
       <c r="R4" t="n">
-        <v>6952220</v>
+        <v>6952049</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,84 +965,66 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974133</t>
+          <t>https://artportalen.se/Sighting/135784572</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111974149</v>
+        <v>111974130</v>
       </c>
       <c r="B5" t="n">
-        <v>93213</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439396</v>
+        <v>439390</v>
       </c>
       <c r="R5" t="n">
-        <v>6952024</v>
+        <v>6952167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,6 +1073,14 @@
           <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
         </is>
       </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # under gammal tallåga</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1153,13 +1099,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974149</t>
+          <t>https://artportalen.se/Sighting/111974130</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111974154</v>
+        <v>111974128</v>
       </c>
       <c r="B6" t="n">
         <v>93213</v>
@@ -1203,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439254</v>
+        <v>439390</v>
       </c>
       <c r="R6" t="n">
-        <v>6952041</v>
+        <v>6952157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,38 +1219,38 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974154</t>
+          <t>https://artportalen.se/Sighting/111974128</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111974122</v>
+        <v>111974133</v>
       </c>
       <c r="B7" t="n">
-        <v>93222</v>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1323,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439233</v>
+        <v>439390</v>
       </c>
       <c r="R7" t="n">
-        <v>6952154</v>
+        <v>6952220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,38 +1339,38 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974122</t>
+          <t>https://artportalen.se/Sighting/111974133</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111974131</v>
+        <v>111974149</v>
       </c>
       <c r="B8" t="n">
-        <v>93222</v>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1443,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439387</v>
+        <v>439396</v>
       </c>
       <c r="R8" t="n">
-        <v>6952179</v>
+        <v>6952024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,38 +1459,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974131</t>
+          <t>https://artportalen.se/Sighting/111974149</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111974136</v>
+        <v>111974154</v>
       </c>
       <c r="B9" t="n">
-        <v>93222</v>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1563,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439426</v>
+        <v>439254</v>
       </c>
       <c r="R9" t="n">
-        <v>6952166</v>
+        <v>6952041</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,16 +1579,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974136</t>
+          <t>https://artportalen.se/Sighting/111974154</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111974138</v>
+        <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>93222</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,43 +1596,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3100</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439542</v>
+        <v>439452</v>
       </c>
       <c r="R10" t="n">
-        <v>6952103</v>
+        <v>6952010</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,12 +1650,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,37 +1666,28 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974138</t>
+          <t>https://artportalen.se/Sighting/135784578</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111974142</v>
+        <v>111974122</v>
       </c>
       <c r="B11" t="n">
         <v>93222</v>
@@ -1803,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439572</v>
+        <v>439233</v>
       </c>
       <c r="R11" t="n">
-        <v>6952035</v>
+        <v>6952154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1873,13 +1801,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974142</t>
+          <t>https://artportalen.se/Sighting/111974122</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111974150</v>
+        <v>111974131</v>
       </c>
       <c r="B12" t="n">
         <v>93222</v>
@@ -1923,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439432</v>
+        <v>439387</v>
       </c>
       <c r="R12" t="n">
-        <v>6952011</v>
+        <v>6952179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,13 +1921,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974150</t>
+          <t>https://artportalen.se/Sighting/111974131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111974157</v>
+        <v>111974136</v>
       </c>
       <c r="B13" t="n">
         <v>93222</v>
@@ -2043,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439240</v>
+        <v>439426</v>
       </c>
       <c r="R13" t="n">
-        <v>6951963</v>
+        <v>6952166</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2113,16 +2041,16 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974157</t>
+          <t>https://artportalen.se/Sighting/111974136</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111974134</v>
+        <v>111974138</v>
       </c>
       <c r="B14" t="n">
-        <v>93189</v>
+        <v>93222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,21 +2058,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2163,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439400</v>
+        <v>439542</v>
       </c>
       <c r="R14" t="n">
-        <v>6952207</v>
+        <v>6952103</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2233,16 +2161,16 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974134</t>
+          <t>https://artportalen.se/Sighting/111974138</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111974143</v>
+        <v>111974142</v>
       </c>
       <c r="B15" t="n">
-        <v>93189</v>
+        <v>93222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,21 +2178,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2283,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439562</v>
+        <v>439572</v>
       </c>
       <c r="R15" t="n">
-        <v>6952045</v>
+        <v>6952035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2353,16 +2281,16 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974143</t>
+          <t>https://artportalen.se/Sighting/111974142</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111974153</v>
+        <v>111974150</v>
       </c>
       <c r="B16" t="n">
-        <v>93189</v>
+        <v>93222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,21 +2298,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2403,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439422</v>
+        <v>439432</v>
       </c>
       <c r="R16" t="n">
-        <v>6951955</v>
+        <v>6952011</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,16 +2401,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974153</t>
+          <t>https://artportalen.se/Sighting/111974150</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103612133</v>
+        <v>111974157</v>
       </c>
       <c r="B17" t="n">
-        <v>93191</v>
+        <v>93222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,21 +2418,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2519,14 +2447,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NV om Gustavbacke, Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439344</v>
+        <v>439240</v>
       </c>
       <c r="R17" t="n">
-        <v>6952209</v>
+        <v>6951963</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2553,12 +2481,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,6 +2497,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2588,16 +2521,16 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103612133</t>
+          <t>https://artportalen.se/Sighting/111974157</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107422373</v>
+        <v>111974134</v>
       </c>
       <c r="B18" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,34 +2538,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439428</v>
+        <v>439400</v>
       </c>
       <c r="R18" t="n">
-        <v>6952170</v>
+        <v>6952207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,12 +2601,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2675,31 +2617,40 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422373</t>
+          <t>https://artportalen.se/Sighting/111974134</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111974123</v>
+        <v>111974143</v>
       </c>
       <c r="B19" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,21 +2658,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2740,10 +2691,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439235</v>
+        <v>439562</v>
       </c>
       <c r="R19" t="n">
-        <v>6952151</v>
+        <v>6952045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2810,16 +2761,16 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974123</t>
+          <t>https://artportalen.se/Sighting/111974143</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111974125</v>
+        <v>111974153</v>
       </c>
       <c r="B20" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,21 +2778,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2860,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439279</v>
+        <v>439422</v>
       </c>
       <c r="R20" t="n">
-        <v>6952207</v>
+        <v>6951955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2930,16 +2881,16 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974125</t>
+          <t>https://artportalen.se/Sighting/111974153</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111974132</v>
+        <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93191</v>
+        <v>93337</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2947,43 +2898,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439385</v>
+        <v>439429</v>
       </c>
       <c r="R21" t="n">
-        <v>6952196</v>
+        <v>6952026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3010,12 +2952,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,37 +2968,28 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974132</t>
+          <t>https://artportalen.se/Sighting/135784577</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111974139</v>
+        <v>103612133</v>
       </c>
       <c r="B22" t="n">
         <v>93191</v>
@@ -3096,14 +3029,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439585</v>
+        <v>439344</v>
       </c>
       <c r="R22" t="n">
-        <v>6952093</v>
+        <v>6952209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3130,12 +3063,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3146,11 +3079,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3170,13 +3098,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974139</t>
+          <t>https://artportalen.se/Sighting/103612133</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111974144</v>
+        <v>107422373</v>
       </c>
       <c r="B23" t="n">
         <v>93191</v>
@@ -3204,26 +3132,17 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439557</v>
+        <v>439428</v>
       </c>
       <c r="R23" t="n">
-        <v>6952049</v>
+        <v>6952170</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3250,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3266,37 +3185,28 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974144</t>
+          <t>https://artportalen.se/Sighting/107422373</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111974151</v>
+        <v>111974123</v>
       </c>
       <c r="B24" t="n">
         <v>93191</v>
@@ -3340,10 +3250,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439457</v>
+        <v>439235</v>
       </c>
       <c r="R24" t="n">
-        <v>6952019</v>
+        <v>6952151</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3410,13 +3320,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974151</t>
+          <t>https://artportalen.se/Sighting/111974123</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111974161</v>
+        <v>111974125</v>
       </c>
       <c r="B25" t="n">
         <v>93191</v>
@@ -3456,14 +3366,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Aloppmoarna i SO, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439131</v>
+        <v>439279</v>
       </c>
       <c r="R25" t="n">
-        <v>6951966</v>
+        <v>6952207</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3530,16 +3440,16 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974161</t>
+          <t>https://artportalen.se/Sighting/111974125</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103612134</v>
+        <v>111974132</v>
       </c>
       <c r="B26" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3547,21 +3457,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3576,14 +3486,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NV om Gustavbacke, Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439308</v>
+        <v>439385</v>
       </c>
       <c r="R26" t="n">
-        <v>6952235</v>
+        <v>6952196</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3610,12 +3520,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3626,6 +3536,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3645,16 +3560,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103612134</t>
+          <t>https://artportalen.se/Sighting/111974132</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103612136</v>
+        <v>111974139</v>
       </c>
       <c r="B27" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3662,21 +3577,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3691,14 +3606,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NV om Gustavbacke, Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439274</v>
+        <v>439585</v>
       </c>
       <c r="R27" t="n">
-        <v>6952201</v>
+        <v>6952093</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3725,12 +3640,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3741,6 +3656,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3760,16 +3680,16 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103612136</t>
+          <t>https://artportalen.se/Sighting/111974139</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103612189</v>
+        <v>111974144</v>
       </c>
       <c r="B28" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3777,21 +3697,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3806,14 +3726,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NV om Gustavbacke, Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439539</v>
+        <v>439557</v>
       </c>
       <c r="R28" t="n">
-        <v>6951909</v>
+        <v>6952049</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3840,12 +3760,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3856,6 +3776,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3875,16 +3800,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103612189</t>
+          <t>https://artportalen.se/Sighting/111974144</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111974124</v>
+        <v>111974151</v>
       </c>
       <c r="B29" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3892,21 +3817,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3925,10 +3850,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439276</v>
+        <v>439457</v>
       </c>
       <c r="R29" t="n">
-        <v>6952197</v>
+        <v>6952019</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3995,16 +3920,16 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974124</t>
+          <t>https://artportalen.se/Sighting/111974151</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111974146</v>
+        <v>111974161</v>
       </c>
       <c r="B30" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4012,21 +3937,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4041,14 +3966,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Aloppmoarna i SO, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439350</v>
+        <v>439131</v>
       </c>
       <c r="R30" t="n">
-        <v>6952064</v>
+        <v>6951966</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4115,13 +4040,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974146</t>
+          <t>https://artportalen.se/Sighting/111974161</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111974160</v>
+        <v>103612134</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -4161,14 +4086,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Aloppmoarna i SO, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439162</v>
+        <v>439308</v>
       </c>
       <c r="R31" t="n">
-        <v>6951960</v>
+        <v>6952235</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4195,12 +4120,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4211,11 +4136,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4235,16 +4155,16 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974160</t>
+          <t>https://artportalen.se/Sighting/103612134</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107422372</v>
+        <v>103612136</v>
       </c>
       <c r="B32" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4252,34 +4172,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439455</v>
+        <v>439274</v>
       </c>
       <c r="R32" t="n">
-        <v>6952113</v>
+        <v>6952201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4306,12 +4235,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,27 +4255,31 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107422372</t>
+          <t>https://artportalen.se/Sighting/103612136</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111974127</v>
+        <v>103612189</v>
       </c>
       <c r="B33" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4354,21 +4287,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4383,14 +4316,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>NV om Gustavbacke, Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439300</v>
+        <v>439539</v>
       </c>
       <c r="R33" t="n">
-        <v>6952178</v>
+        <v>6951909</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4417,12 +4350,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4433,11 +4366,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4457,16 +4385,16 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974127</t>
+          <t>https://artportalen.se/Sighting/103612189</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111974140</v>
+        <v>111974124</v>
       </c>
       <c r="B34" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4474,21 +4402,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4507,10 +4435,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439585</v>
+        <v>439276</v>
       </c>
       <c r="R34" t="n">
-        <v>6952093</v>
+        <v>6952197</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4577,16 +4505,16 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974140</t>
+          <t>https://artportalen.se/Sighting/111974124</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111974159</v>
+        <v>111974146</v>
       </c>
       <c r="B35" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,21 +4522,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4623,14 +4551,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Aloppmoarna i SO, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439166</v>
+        <v>439350</v>
       </c>
       <c r="R35" t="n">
-        <v>6951948</v>
+        <v>6952064</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4697,16 +4625,16 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974159</t>
+          <t>https://artportalen.se/Sighting/111974146</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111974162</v>
+        <v>111974160</v>
       </c>
       <c r="B36" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4714,21 +4642,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4747,7 +4675,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439105</v>
+        <v>439162</v>
       </c>
       <c r="R36" t="n">
         <v>6951960</v>
@@ -4817,16 +4745,16 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974162</t>
+          <t>https://artportalen.se/Sighting/111974160</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111974129</v>
+        <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>92841</v>
+        <v>93345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,43 +4762,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439390</v>
+        <v>439372</v>
       </c>
       <c r="R37" t="n">
-        <v>6952167</v>
+        <v>6952030</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4897,12 +4816,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4913,40 +4832,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974129</t>
+          <t>https://artportalen.se/Sighting/135784575</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111974135</v>
+        <v>107422372</v>
       </c>
       <c r="B38" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4954,43 +4864,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439406</v>
+        <v>439455</v>
       </c>
       <c r="R38" t="n">
-        <v>6952200</v>
+        <v>6952113</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5017,12 +4918,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5033,62 +4934,53 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974135</t>
+          <t>https://artportalen.se/Sighting/107422372</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111974126</v>
+        <v>111974127</v>
       </c>
       <c r="B39" t="n">
-        <v>90691</v>
+        <v>93209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5107,10 +4999,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439290</v>
+        <v>439300</v>
       </c>
       <c r="R39" t="n">
-        <v>6952209</v>
+        <v>6952178</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5177,38 +5069,38 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974126</t>
+          <t>https://artportalen.se/Sighting/111974127</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111974137</v>
+        <v>111974140</v>
       </c>
       <c r="B40" t="n">
-        <v>90691</v>
+        <v>93209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5227,10 +5119,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439438</v>
+        <v>439585</v>
       </c>
       <c r="R40" t="n">
-        <v>6952140</v>
+        <v>6952093</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5297,38 +5189,38 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974137</t>
+          <t>https://artportalen.se/Sighting/111974140</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111974145</v>
+        <v>111974159</v>
       </c>
       <c r="B41" t="n">
-        <v>90691</v>
+        <v>93209</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5343,14 +5235,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Aloppmoarna i SO, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439522</v>
+        <v>439166</v>
       </c>
       <c r="R41" t="n">
-        <v>6952046</v>
+        <v>6951948</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5417,38 +5309,38 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974145</t>
+          <t>https://artportalen.se/Sighting/111974159</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111974147</v>
+        <v>111974162</v>
       </c>
       <c r="B42" t="n">
-        <v>90691</v>
+        <v>93209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5463,14 +5355,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Aloppmoarna i SO, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439342</v>
+        <v>439105</v>
       </c>
       <c r="R42" t="n">
-        <v>6952056</v>
+        <v>6951960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5537,38 +5429,38 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974147</t>
+          <t>https://artportalen.se/Sighting/111974162</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111974148</v>
+        <v>111974129</v>
       </c>
       <c r="B43" t="n">
-        <v>90691</v>
+        <v>92841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5587,10 +5479,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439399</v>
+        <v>439390</v>
       </c>
       <c r="R43" t="n">
-        <v>6952034</v>
+        <v>6952167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,38 +5549,38 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974148</t>
+          <t>https://artportalen.se/Sighting/111974129</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111974152</v>
+        <v>111974135</v>
       </c>
       <c r="B44" t="n">
-        <v>90691</v>
+        <v>92841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5707,10 +5599,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439457</v>
+        <v>439406</v>
       </c>
       <c r="R44" t="n">
-        <v>6952019</v>
+        <v>6952200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5777,60 +5669,51 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974152</t>
+          <t>https://artportalen.se/Sighting/111974135</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111974155</v>
+        <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>90691</v>
+        <v>92509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6276</v>
+        <v>5467</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Aloppmoarna i S, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439255</v>
+        <v>439453</v>
       </c>
       <c r="R45" t="n">
-        <v>6952037</v>
+        <v>6952013</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5857,12 +5740,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5873,37 +5756,28 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974155</t>
+          <t>https://artportalen.se/Sighting/135784579</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111974158</v>
+        <v>111974126</v>
       </c>
       <c r="B46" t="n">
         <v>90691</v>
@@ -5947,10 +5821,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439236</v>
+        <v>439290</v>
       </c>
       <c r="R46" t="n">
-        <v>6951939</v>
+        <v>6952209</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6017,51 +5891,60 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111974158</t>
+          <t>https://artportalen.se/Sighting/111974126</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>107422371</v>
+        <v>111974137</v>
       </c>
       <c r="B47" t="n">
-        <v>58114</v>
+        <v>90691</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6276</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Aloppmoarna i S, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439557</v>
+        <v>439438</v>
       </c>
       <c r="R47" t="n">
-        <v>6952016</v>
+        <v>6952140</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6088,12 +5971,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6104,22 +5987,1363 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974137</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>111974145</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>439522</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6952046</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974145</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>111974147</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>439342</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6952056</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974147</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>111974148</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>439399</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6952034</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974148</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>111974152</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>439457</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6952019</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974152</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>111974155</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>439255</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6952037</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974155</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>111974158</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Aloppmoarna i S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>439236</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6951939</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>äldre renbetad ristallskog med lavfläckar på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111974158</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135784568</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>439133</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6952008</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784568</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135784569</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>439114</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6952000</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784569</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>107422371</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>439557</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6952016</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX56" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107422371</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135784567</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>439128</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6951969</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784567</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135784570</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>439266</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6952044</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784570</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135784576</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>439377</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6952035</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784576</t>
         </is>
       </c>
     </row>
@@ -6171,6 +7395,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92509</v>
+        <v>92511</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92445</v>
+        <v>92459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92511</v>
+        <v>92525</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135784568</v>
       </c>
       <c r="B54" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>135784569</v>
       </c>
       <c r="B55" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135784567</v>
       </c>
       <c r="B57" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135784570</v>
       </c>
       <c r="B58" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>135784576</v>
       </c>
       <c r="B59" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92525</v>
+        <v>92526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135784568</v>
       </c>
       <c r="B54" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>135784569</v>
       </c>
       <c r="B55" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135784567</v>
       </c>
       <c r="B57" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135784570</v>
       </c>
       <c r="B58" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>135784576</v>
       </c>
       <c r="B59" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92526</v>
+        <v>92527</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135784568</v>
       </c>
       <c r="B54" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>135784569</v>
       </c>
       <c r="B55" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135784567</v>
       </c>
       <c r="B57" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135784570</v>
       </c>
       <c r="B58" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>135784576</v>
       </c>
       <c r="B59" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92462</v>
+        <v>92468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92528</v>
+        <v>92534</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135784568</v>
       </c>
       <c r="B54" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>135784569</v>
       </c>
       <c r="B55" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135784567</v>
       </c>
       <c r="B57" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135784570</v>
       </c>
       <c r="B58" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>135784576</v>
       </c>
       <c r="B59" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92468</v>
+        <v>92469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92534</v>
+        <v>92535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135784568</v>
       </c>
       <c r="B54" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>135784569</v>
       </c>
       <c r="B55" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135784567</v>
       </c>
       <c r="B57" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135784570</v>
       </c>
       <c r="B58" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>135784576</v>
       </c>
       <c r="B59" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92469</v>
+        <v>92475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92535</v>
+        <v>92541</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135784568</v>
       </c>
       <c r="B54" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>135784569</v>
       </c>
       <c r="B55" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135784567</v>
       </c>
       <c r="B57" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135784570</v>
       </c>
       <c r="B58" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>135784576</v>
       </c>
       <c r="B59" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92475</v>
+        <v>92482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784574</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92541</v>
+        <v>92548</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135784568</v>
       </c>
       <c r="B54" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>135784569</v>
       </c>
       <c r="B55" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>135784567</v>
       </c>
       <c r="B57" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135784570</v>
       </c>
       <c r="B58" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>135784576</v>
       </c>
       <c r="B59" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 56437-2025 artfynd.xlsx
+++ b/artfynd/A 56437-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784573</v>
       </c>
       <c r="B2" t="n">
-        <v>92482</v>
+        <v>92483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784572</v>
       </c>
       <c r="B4" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135784578</v>
       </c>
       <c r="B10" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>135784577</v>
       </c>
       <c r="B21" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135784575</v>
       </c>
       <c r="B37" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135784579</v>
       </c>
       <c r="B45" t="n">
-        <v>92548</v>
+        <v>92549</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
